--- a/Data/taxonomy/taxonomy.xlsx
+++ b/Data/taxonomy/taxonomy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/llew0024/Dropbox/Devonian fish/species/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/llew0024/Dropbox/Global Ecology Lab/research/Fish networks/taxonomy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EB88E9-1978-4141-96C7-BA2824F3DEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115EC77E-EA72-344C-BCEB-3A484F5D14E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18980" xr2:uid="{F19CBC05-0EDB-114B-8D9B-7ABD95CB3354}"/>
+    <workbookView xWindow="520" yWindow="960" windowWidth="33600" windowHeight="18980" xr2:uid="{F19CBC05-0EDB-114B-8D9B-7ABD95CB3354}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="245">
   <si>
     <t>taxon</t>
   </si>
@@ -735,6 +735,84 @@
   </si>
   <si>
     <t>Simosteus</t>
+  </si>
+  <si>
+    <t>Bothriolepis yeungae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remigolepis walkeri </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groenlandaspis sp. </t>
+  </si>
+  <si>
+    <t>Soederberghia simpsoni</t>
+  </si>
+  <si>
+    <t>Gooloogongia loomesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canowindra grossi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mandageria fairfaxi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabonnichthys burnsi </t>
+  </si>
+  <si>
+    <t>Canowindra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bothriolepis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remigolepis  </t>
+  </si>
+  <si>
+    <t>Remigolepidae</t>
+  </si>
+  <si>
+    <t>Groenlandaspis</t>
+  </si>
+  <si>
+    <t>Groenlandaspididae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arthrodira </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soederberghia </t>
+  </si>
+  <si>
+    <t>Rhynchodipteridae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gooloogongia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhizodont </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tetrapodomorpha </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canowindra  </t>
+  </si>
+  <si>
+    <t>Canowindrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mandageria  </t>
+  </si>
+  <si>
+    <t>Tristichopterid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabonnichthys  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristichopterid </t>
   </si>
 </sst>
 </file>
@@ -866,7 +944,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -886,6 +964,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -1201,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{670C1D04-0CE9-B048-A707-5827B64F4CF8}">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="28.5" style="2" customWidth="1"/>
@@ -2918,6 +2997,175 @@
         <v>199</v>
       </c>
     </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B78" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="C78" t="s">
+        <v>228</v>
+      </c>
+      <c r="D78" t="s">
+        <v>80</v>
+      </c>
+      <c r="E78" t="s">
+        <v>81</v>
+      </c>
+      <c r="F78" t="s">
+        <v>130</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B79" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C79" t="s">
+        <v>229</v>
+      </c>
+      <c r="D79" t="s">
+        <v>230</v>
+      </c>
+      <c r="E79" t="s">
+        <v>81</v>
+      </c>
+      <c r="F79" t="s">
+        <v>130</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="C80" t="s">
+        <v>231</v>
+      </c>
+      <c r="D80" t="s">
+        <v>232</v>
+      </c>
+      <c r="E80" t="s">
+        <v>233</v>
+      </c>
+      <c r="F80" t="s">
+        <v>132</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B81" t="s">
+        <v>222</v>
+      </c>
+      <c r="C81" t="s">
+        <v>234</v>
+      </c>
+      <c r="D81" t="s">
+        <v>235</v>
+      </c>
+      <c r="F81" t="s">
+        <v>121</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B82" t="s">
+        <v>223</v>
+      </c>
+      <c r="C82" t="s">
+        <v>236</v>
+      </c>
+      <c r="E82" t="s">
+        <v>237</v>
+      </c>
+      <c r="F82" t="s">
+        <v>238</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B83" t="s">
+        <v>224</v>
+      </c>
+      <c r="C83" t="s">
+        <v>239</v>
+      </c>
+      <c r="E83" t="s">
+        <v>240</v>
+      </c>
+      <c r="F83" t="s">
+        <v>238</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B84" t="s">
+        <v>225</v>
+      </c>
+      <c r="C84" t="s">
+        <v>241</v>
+      </c>
+      <c r="E84" t="s">
+        <v>242</v>
+      </c>
+      <c r="F84" t="s">
+        <v>238</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B85" t="s">
+        <v>226</v>
+      </c>
+      <c r="C85" t="s">
+        <v>243</v>
+      </c>
+      <c r="E85" t="s">
+        <v>244</v>
+      </c>
+      <c r="F85" t="s">
+        <v>238</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
